--- a/ig/DM-AVRIL-2026/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="275">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260202120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -786,6 +786,12 @@
   </si>
   <si>
     <t>Synthèse Salle de Naissance Enfant</t>
+  </si>
+  <si>
+    <t>84067-8</t>
+  </si>
+  <si>
+    <t>Synthèse transfusionnelle</t>
   </si>
   <si>
     <t>89235-6</t>
@@ -1413,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2102,18 +2108,26 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>98</v>
+        <v>269</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>98</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="B87" t="s" s="2">
-        <v>269</v>
+      <c r="B88" t="s" s="2">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -2140,10 +2154,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3">
@@ -2159,7 +2173,7 @@
         <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
